--- a/assets/plantillas/TIC-FRM-003.xlsx
+++ b/assets/plantillas/TIC-FRM-003.xlsx
@@ -595,6 +595,31 @@
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>571500</rowOff>
+    </from>
+    <ext cx="3048000" cy="600075"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -923,7 +948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O60"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.8984375" defaultRowHeight="13.8"/>
   <cols>
     <col width="4.3984375" customWidth="1" style="1" min="1" max="1"/>

--- a/assets/plantillas/TIC-FRM-003.xlsx
+++ b/assets/plantillas/TIC-FRM-003.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EQ Soluciones\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EQSoluciones\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF57AA0-6830-475B-97D6-73FA4A2081C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9A5C167-7E93-495D-8EC7-9FA486F26C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="684" yWindow="480" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Formulario (31)" sheetId="1" r:id="rId1"/>
@@ -254,7 +254,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -263,16 +265,10 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -280,6 +276,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -298,7 +295,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -312,6 +309,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -376,18 +376,18 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>647428</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>150494</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>801055</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>261259</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2136322" cy="1764302"/>
+    <xdr:ext cx="2377572" cy="468085"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagen 2">
+        <xdr:cNvPr id="4" name="Image 3" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A475B72-ACD1-4470-9A68-AB183BBD14AF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -396,22 +396,19 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4544514" y="8064408"/>
-          <a:ext cx="2136322" cy="1764302"/>
+          <a:off x="11316655" y="435430"/>
+          <a:ext cx="2377572" cy="468085"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -765,84 +762,84 @@
     </row>
     <row r="2" spans="1:13" ht="21.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>ACTA RECEPCIÓN ADQUISICIÓN TECNOLÓGICA
 Tecnología, Información &amp; Comunicaciones
 TIC-FRM-003</t>
         </is>
       </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
     </row>
     <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
-      <c r="B3" s="22"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="23"/>
-      <c r="M3" s="23"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="23"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="21"/>
     </row>
     <row r="6" spans="1:13" ht="10.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
     </row>
     <row r="7" spans="1:13" ht="10.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12"/>
@@ -883,7 +880,7 @@
       <c r="M10" s="16"/>
     </row>
     <row r="11" spans="1:13" s="5" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
@@ -905,7 +902,7 @@
       <c r="M11" s="16"/>
     </row>
     <row r="12" spans="1:13" s="5" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
@@ -950,7 +947,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>Item solicitado (Marca, modelo, servicio)</t>
         </is>
@@ -1225,60 +1222,60 @@
       <c r="M27" s="16"/>
     </row>
     <row r="28" spans="2:13" s="5" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="27"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="28"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="28"/>
-      <c r="M28" s="29"/>
+      <c r="B28" s="26"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="27"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="27"/>
+      <c r="M28" s="28"/>
     </row>
     <row r="29" spans="2:13" s="5" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="30"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="31"/>
-      <c r="L29" s="31"/>
-      <c r="M29" s="32"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="31"/>
     </row>
     <row r="30" spans="2:13" s="5" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="30"/>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="31"/>
-      <c r="I30" s="31"/>
-      <c r="J30" s="31"/>
-      <c r="K30" s="31"/>
-      <c r="L30" s="31"/>
-      <c r="M30" s="32"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="30"/>
+      <c r="M30" s="31"/>
     </row>
     <row r="31" spans="2:13" s="5" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="30"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="31"/>
-      <c r="I31" s="31"/>
-      <c r="J31" s="31"/>
-      <c r="K31" s="31"/>
-      <c r="L31" s="31"/>
-      <c r="M31" s="32"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="31"/>
     </row>
     <row r="32" spans="2:13" s="5" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="17" t="inlineStr">
@@ -1299,16 +1296,16 @@
       <c r="M32" s="16"/>
     </row>
     <row r="33" spans="2:13" s="5" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="33" t="inlineStr">
+      <c r="B33" s="32" t="inlineStr">
         <is>
           <t>ENTREGA</t>
         </is>
       </c>
-      <c r="C33" s="34"/>
-      <c r="D33" s="34"/>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
-      <c r="G33" s="35"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="34"/>
       <c r="H33" s="17" t="inlineStr">
         <is>
           <t>DEVOLUCIÓN</t>
@@ -1321,84 +1318,84 @@
       <c r="M33" s="15"/>
     </row>
     <row r="34" spans="2:13" s="5" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19"/>
-      <c r="K34" s="19"/>
-      <c r="L34" s="19"/>
-      <c r="M34" s="19"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="35"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="35"/>
     </row>
     <row r="35" spans="2:13" s="5" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="20"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="19"/>
-      <c r="J35" s="19"/>
-      <c r="K35" s="19"/>
-      <c r="L35" s="19"/>
-      <c r="M35" s="19"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="35"/>
+      <c r="J35" s="35"/>
+      <c r="K35" s="35"/>
+      <c r="L35" s="35"/>
+      <c r="M35" s="35"/>
     </row>
     <row r="36" spans="2:13" s="5" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="20" t="inlineStr">
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>{{FIRMA_USUARIO}}</t>
         </is>
       </c>
-      <c r="C36" s="20"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20" t="inlineStr">
-        <is>
-          <t>Soporte técnico: OSCAR RAMIREZ V</t>
-        </is>
-      </c>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20" t="inlineStr">
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>{{SOPORTE_ENTREGA}}</t>
+        </is>
+      </c>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13" t="inlineStr">
         <is>
           <t>{{FIRMA_USUARIO}}</t>
         </is>
       </c>
-      <c r="I36" s="20"/>
-      <c r="J36" s="20"/>
-      <c r="K36" s="20" t="inlineStr">
-        <is>
-          <t>Soporte técnico: OSCAR RAMIREZ V</t>
-        </is>
-      </c>
-      <c r="L36" s="20"/>
-      <c r="M36" s="20"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13" t="inlineStr">
+        <is>
+          <t>{{SOPORTE_DEVOLUCION}}</t>
+        </is>
+      </c>
+      <c r="L36" s="13"/>
+      <c r="M36" s="13"/>
     </row>
     <row r="37" spans="2:13" s="5" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="20" t="inlineStr">
+      <c r="B37" s="13" t="inlineStr">
         <is>
           <t>{{FECHA_FIRMA}}</t>
         </is>
       </c>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20" t="inlineStr">
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13" t="inlineStr">
         <is>
           <t>{{FECHA_DEVOLUCION}}</t>
         </is>
       </c>
-      <c r="I37" s="20"/>
-      <c r="J37" s="20"/>
-      <c r="K37" s="20"/>
-      <c r="L37" s="20"/>
-      <c r="M37" s="20"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
+      <c r="M37" s="13"/>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C38" s="4"/>
@@ -1479,11 +1476,6 @@
     <mergeCell ref="E34:G35"/>
     <mergeCell ref="H34:J35"/>
     <mergeCell ref="K34:M35"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="D12:M12"/>
     <mergeCell ref="B2:M6"/>
     <mergeCell ref="C15:M15"/>
     <mergeCell ref="C24:M24"/>
@@ -1491,10 +1483,10 @@
     <mergeCell ref="C14:M14"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B10:M10"/>
-    <mergeCell ref="C26:M26"/>
     <mergeCell ref="C20:M20"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:M11"/>
+    <mergeCell ref="D12:M12"/>
     <mergeCell ref="B37:G37"/>
     <mergeCell ref="C25:M25"/>
     <mergeCell ref="H37:M37"/>
@@ -1506,10 +1498,15 @@
     <mergeCell ref="C19:M19"/>
     <mergeCell ref="B21:M21"/>
     <mergeCell ref="C18:M18"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="C26:M26"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="60" orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" scale="60" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>